--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T15:26:54+00:00</t>
+    <t>2025-01-23T13:26:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-23T13:26:37+00:00</t>
+    <t>2025-01-24T17:22:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-24T17:22:23+00:00</t>
+    <t>2025-01-29T14:25:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-29T14:25:50+00:00</t>
+    <t>2025-01-29T15:50:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-29T15:50:40+00:00</t>
+    <t>2025-01-30T15:03:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-30T15:03:39+00:00</t>
+    <t>2025-01-31T08:45:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-31T08:45:39+00:00</t>
+    <t>2025-02-18T10:06:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="140">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T10:06:11+00:00</t>
+    <t>2025-02-18T11:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>DataEnterer contient les informations relatives à l’opérateur de saisie de tout ou partie du contenu du document.</t>
+    <t>L'élément de l'en-tête du CDA dataEnterer contient les informations relatives à l’opérateur de saisie de tout ou partie du contenu du document.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -413,11 +413,36 @@
 </t>
   </si>
   <si>
+    <t>Horodatage de la participation de l’opérateur.</t>
+  </si>
+  <si>
+    <t>DataEnterer.time.nullFlavor</t>
+  </si>
+  <si>
+    <t>DataEnterer.time.value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime {http://hl7.org/cda/stds/core/StructureDefinition/ts-simple}
+</t>
+  </si>
+  <si>
+    <t>Date et heure à laquelle l’opérateur a participé à l’élaboration du document.</t>
+  </si>
+  <si>
+    <t>A quantity specifying a point on the axis of natural time. A point in time is most often represented as a calendar expression.</t>
+  </si>
+  <si>
+    <t>TS.value</t>
+  </si>
+  <si>
     <t>DataEnterer.assignedEntity</t>
   </si>
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/AssignedEntity {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-assigned-entity}
 </t>
+  </si>
+  <si>
+    <t>Personne physique.</t>
   </si>
 </sst>
 </file>
@@ -719,7 +744,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK15"/>
+  <dimension ref="A1:AK17"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="41.7890625" customWidth="true" bestFit="true"/>
@@ -2117,7 +2142,9 @@
       <c r="K14" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="L14" s="2"/>
+      <c r="L14" t="s" s="2">
+        <v>130</v>
+      </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2188,18 +2215,20 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E15" s="2"/>
+      <c r="E15" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F15" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>75</v>
@@ -2214,10 +2243,12 @@
         <v>74</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>131</v>
+        <v>85</v>
       </c>
       <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
+      <c r="M15" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -2243,13 +2274,11 @@
         <v>74</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y15" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y15" s="2"/>
       <c r="Z15" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>74</v>
@@ -2267,10 +2296,10 @@
         <v>74</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>130</v>
+        <v>89</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH15" t="s" s="2">
         <v>75</v>
@@ -2282,6 +2311,210 @@
         <v>74</v>
       </c>
       <c r="AK15" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E16" s="2"/>
+      <c r="F16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G16" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K16" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q16" s="2"/>
+      <c r="R16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF16" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AG16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH16" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK16" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E17" s="2"/>
+      <c r="F17" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G17" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K17" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q17" s="2"/>
+      <c r="R17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF17" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AG17" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK17" t="s" s="2">
         <v>74</v>
       </c>
     </row>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T11:00:40+00:00</t>
+    <t>2025-02-18T15:10:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:10:02+00:00</t>
+    <t>2025-02-18T15:17:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:17:48+00:00</t>
+    <t>2025-02-18T15:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:18:09+00:00</t>
+    <t>2025-02-18T15:18:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:18:38+00:00</t>
+    <t>2025-02-18T15:24:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:24:54+00:00</t>
+    <t>2025-02-18T15:28:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:28:32+00:00</t>
+    <t>2025-02-18T15:29:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:29:38+00:00</t>
+    <t>2025-02-18T15:30:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:04+00:00</t>
+    <t>2025-02-18T15:30:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:23+00:00</t>
+    <t>2025-02-18T15:30:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:53+00:00</t>
+    <t>2025-02-20T13:34:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:34:17+00:00</t>
+    <t>2025-02-20T13:46:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:46:00+00:00</t>
+    <t>2025-02-20T13:48:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:48:47+00:00</t>
+    <t>2025-02-20T13:50:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:50:16+00:00</t>
+    <t>2025-02-20T13:50:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:50:51+00:00</t>
+    <t>2025-02-20T13:51:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:51:52+00:00</t>
+    <t>2025-02-20T13:53:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:53:17+00:00</t>
+    <t>2025-02-20T13:53:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:53:53+00:00</t>
+    <t>2025-02-20T14:37:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:37:28+00:00</t>
+    <t>2025-02-20T14:38:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:38:00+00:00</t>
+    <t>2025-02-20T14:38:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:38:23+00:00</t>
+    <t>2025-02-20T14:42:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:42:14+00:00</t>
+    <t>2025-02-20T14:42:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:42:55+00:00</t>
+    <t>2025-02-20T14:43:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:43:30+00:00</t>
+    <t>2025-02-20T14:45:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:45:32+00:00</t>
+    <t>2025-02-20T14:47:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:47:06+00:00</t>
+    <t>2025-02-20T14:48:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:48:16+00:00</t>
+    <t>2025-02-20T15:31:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T15:31:18+00:00</t>
+    <t>2025-02-21T13:12:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-21T13:12:29+00:00</t>
+    <t>2025-02-21T15:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-21T15:18:09+00:00</t>
+    <t>2025-02-23T14:02:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-23T14:02:58+00:00</t>
+    <t>2025-02-24T10:33:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T10:33:29+00:00</t>
+    <t>2025-02-24T11:08:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T11:08:59+00:00</t>
+    <t>2025-02-24T14:08:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-data-enterer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T14:08:41+00:00</t>
+    <t>2025-02-25T09:00:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
